--- a/artfynd/A 49914-2021 artfynd.xlsx
+++ b/artfynd/A 49914-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49914-2021 artfynd.xlsx
+++ b/artfynd/A 49914-2021 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70430924</v>
+        <v>108828495</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marsjön, Storsjön vid Sölvik, Dls</t>
+          <t>Torstjärnet, NV om, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339322.7212285026</v>
+        <v>339407</v>
       </c>
       <c r="R2" t="n">
-        <v>6521833.523984047</v>
+        <v>6521639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca 125 moh</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bergvägg vid insjö.</t>
+          <t>Barrdominerad blandskog i delvis avverkat område.</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>På sten/tunt jordtäcke.</t>
+          <t>Murken låga, troligen gran.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>70430907</v>
+        <v>108828496</v>
       </c>
       <c r="B3" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Marsjön, Storsjön vid Sölvik, Dls</t>
+          <t>Torstjärnet, NV om, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339322.7212285026</v>
+        <v>339407</v>
       </c>
       <c r="R3" t="n">
-        <v>6521833.523984047</v>
+        <v>6521639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,27 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca 125 moh</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,12 +866,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Bergvägg vid insjö.</t>
+          <t>Barrdominerad blandskog i delvis avverkat område.</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På sten/tunt jordtäcke.</t>
+          <t>Murken låga, troligen gran.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -929,50 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>70430897</v>
+        <v>108917265</v>
       </c>
       <c r="B4" t="n">
-        <v>95220</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2609</v>
+        <v>54</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Marsjön, Storsjön vid Sölvik, Dls</t>
+          <t>Torstjärnet, NV om, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339322.7212285026</v>
+        <v>339272</v>
       </c>
       <c r="R4" t="n">
-        <v>6521833.523984047</v>
+        <v>6521650</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,27 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 125 moh</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,17 +972,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Bergvägg vid insjö.</t>
+          <t>Nyligen kalhuggen 150 år gammal granskog.</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På sten/tunt jordtäcke.</t>
+          <t>Murken låga, troligen gran.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,50 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70430846</v>
+        <v>108828494</v>
       </c>
       <c r="B5" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>1841</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Marsjön, Storsjön vid Sölvik, Dls</t>
+          <t>Torstjärnet, NV om, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339322.7212285026</v>
+        <v>339407</v>
       </c>
       <c r="R5" t="n">
-        <v>6521833.523984047</v>
+        <v>6521639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,27 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 125 moh</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,12 +1085,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bergvägg vid insjö.</t>
+          <t>Barrdominerad blandskog i delvis avverkat område.</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På sten/tunt jordtäcke.</t>
+          <t>Murken låga, troligen gran.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1183,15 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>70430893</v>
+        <v>108828491</v>
       </c>
       <c r="B6" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,34 +1119,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2779</v>
+        <v>2389</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Hook.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Marsjön, Storsjön vid Sölvik, Dls</t>
+          <t>Torstjärnet, NV om, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339322.7212285026</v>
+        <v>339308</v>
       </c>
       <c r="R6" t="n">
-        <v>6521833.523984047</v>
+        <v>6521659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,27 +1185,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca 125 moh</t>
+          <t>Nyligen kalhugget framför bergväggen, så arten kommer troligen att försvinna från lokalen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,17 +1204,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bergvägg vid insjö.</t>
+          <t>Nyligen kalavverkad 150 år gammal granskog!!!</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På sten/tunt jordtäcke.</t>
+          <t>På nordvänd bergvägg</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1310,15 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70430909</v>
+        <v>108828487</v>
       </c>
       <c r="B7" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,34 +1244,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Marsjön, Storsjön vid Sölvik, Dls</t>
+          <t>Torstjärnet, NV om, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339322.7212285026</v>
+        <v>339272</v>
       </c>
       <c r="R7" t="n">
-        <v>6521833.523984047</v>
+        <v>6521650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,27 +1302,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-03-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 125 moh</t>
+          <t>Riklig förekomst på bergvägg längs ca. 40 meter. Nyligen kalhugget framför, så arten kommer troligen att försvinna från lokalen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,17 +1321,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Bergvägg vid insjö.</t>
+          <t>Nyligen kalavverkad 150 år gammal granskog!!!</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På sten/tunt jordtäcke.</t>
+          <t>På nordvänd bergvägg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1437,50 +1350,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>108828495</v>
+        <v>108828492</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Torstjärnet, NV om, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339406.0783546612</v>
+        <v>339308</v>
       </c>
       <c r="R8" t="n">
-        <v>6521638.666072479</v>
+        <v>6521659</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1510,19 +1422,14 @@
           <t>2023-05-06</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-05-06</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig förekomst på bergvägg längs ca. 40 meter. Nyligen kalhugget framför, så arten kommer troligen att försvinna från lokalen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,17 +1438,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerad blandskog i delvis avverkat område.</t>
+          <t>Nyligen kalavverkad 150 år gammal granskog!!!</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Murken låga, troligen gran.</t>
+          <t>På nordvänd bergvägg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1559,50 +1467,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108828496</v>
+        <v>70430846</v>
       </c>
       <c r="B9" t="n">
-        <v>94112</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>2606</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Torstjärnet, NV om, Dls</t>
+          <t>Marsjön, Storsjön vid Sölvik, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>339406.0783546612</v>
+        <v>339323</v>
       </c>
       <c r="R9" t="n">
-        <v>6521638.666072479</v>
+        <v>6521834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,22 +1532,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 125 moh</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,12 +1556,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerad blandskog i delvis avverkat område.</t>
+          <t>Bergvägg vid insjö.</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Murken låga, troligen gran.</t>
+          <t>På sten/tunt jordtäcke.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1681,15 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108828492</v>
+        <v>70430897</v>
       </c>
       <c r="B10" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,38 +1590,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>2609</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Torstjärnet, NV om, Dls</t>
+          <t>Marsjön, Storsjön vid Sölvik, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339308.1850812279</v>
+        <v>339323</v>
       </c>
       <c r="R10" t="n">
-        <v>6521658.813155076</v>
+        <v>6521834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1755,27 +1644,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Riklig förekomst på bergvägg längs ca. 40 meter. Nyligen kalhugget framför, så arten kommer troligen att försvinna från lokalen.</t>
+          <t>Ca 125 moh</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1784,18 +1663,17 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Nyligen kalavverkad 150 år gammal granskog!!!</t>
+          <t>Bergvägg vid insjö.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>På nordvänd bergvägg</t>
+          <t>På sten/tunt jordtäcke.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1813,15 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>108828491</v>
+        <v>70430909</v>
       </c>
       <c r="B11" t="n">
-        <v>95187</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,46 +1702,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2389</v>
+        <v>2667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Torstjärnet, NV om, Dls</t>
+          <t>Marsjön, Storsjön vid Sölvik, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339308.1850812279</v>
+        <v>339323</v>
       </c>
       <c r="R11" t="n">
-        <v>6521658.813155076</v>
+        <v>6521834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1895,27 +1756,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Nyligen kalhugget framför bergväggen, så arten kommer troligen att försvinna från lokalen.</t>
+          <t>Ca 125 moh</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1924,18 +1775,17 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Nyligen kalavverkad 150 år gammal granskog!!!</t>
+          <t>Bergvägg vid insjö.</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>På nordvänd bergvägg</t>
+          <t>På sten/tunt jordtäcke.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1953,15 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108828487</v>
+        <v>70430924</v>
       </c>
       <c r="B12" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,38 +1814,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>2671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Torstjärnet, NV om, Dls</t>
+          <t>Marsjön, Storsjön vid Sölvik, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339271.9832444126</v>
+        <v>339323</v>
       </c>
       <c r="R12" t="n">
-        <v>6521650.462766904</v>
+        <v>6521834</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2027,27 +1868,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Riklig förekomst på bergvägg längs ca. 40 meter. Nyligen kalhugget framför, så arten kommer troligen att försvinna från lokalen.</t>
+          <t>Ca 125 moh</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2056,18 +1887,17 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Nyligen kalavverkad 150 år gammal granskog!!!</t>
+          <t>Bergvägg vid insjö.</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>På nordvänd bergvägg</t>
+          <t>På sten/tunt jordtäcke.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2085,50 +1915,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108828494</v>
+        <v>70430893</v>
       </c>
       <c r="B13" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1841</v>
+        <v>2779</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Torstjärnet, NV om, Dls</t>
+          <t>Marsjön, Storsjön vid Sölvik, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339406.0783546612</v>
+        <v>339323</v>
       </c>
       <c r="R13" t="n">
-        <v>6521638.666072479</v>
+        <v>6521834</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2155,22 +1980,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ca 125 moh</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2184,12 +2004,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrdominerad blandskog i delvis avverkat område.</t>
+          <t>Bergvägg vid insjö.</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Murken låga, troligen gran.</t>
+          <t>På sten/tunt jordtäcke.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2207,54 +2027,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108917265</v>
+        <v>70430907</v>
       </c>
       <c r="B14" t="n">
-        <v>94112</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Torstjärnet, NV om, Dls</t>
+          <t>Marsjön, Storsjön vid Sölvik, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>339271.9832444126</v>
+        <v>339323</v>
       </c>
       <c r="R14" t="n">
-        <v>6521650.462766904</v>
+        <v>6521834</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2281,22 +2092,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ca 125 moh</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2305,18 +2111,17 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Nyligen kalhuggen 150 år gammal granskog.</t>
+          <t>Bergvägg vid insjö.</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Murken låga, troligen gran.</t>
+          <t>På sten/tunt jordtäcke.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 49914-2021 artfynd.xlsx
+++ b/artfynd/A 49914-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108828495</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108828496</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108917265</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108828494</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108828491</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108828487</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,6 +1499,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108828492</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70430846</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,6 +1733,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70430897</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1800,6 +1850,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70430909</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70430924</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2024,6 +2084,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70430893</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2136,8 +2201,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70430907</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>